--- a/AAII_Financials/Yearly/CENN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CENN_YR_FIN.xlsx
@@ -953,7 +953,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>34600</v>
+        <v>36400</v>
       </c>
       <c r="E14" s="3">
         <v>1800</v>
@@ -1154,7 +1154,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1300</v>
+        <v>-500</v>
       </c>
       <c r="E20" s="3">
         <v>500</v>
@@ -1196,7 +1196,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-31700</v>
+        <v>-29900</v>
       </c>
       <c r="E21" s="3">
         <v>-30100</v>
@@ -1658,7 +1658,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1300</v>
+        <v>500</v>
       </c>
       <c r="E32" s="3">
         <v>-500</v>
